--- a/templates/kits_template.xlsx
+++ b/templates/kits_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sasha\YandexDisk\WB\Расчет поставок и закупок\Поставки\Остатки\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C204385-D797-4122-A691-49D28AC7DDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D153980-E1A6-4E58-9E38-59170D489990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-107" yWindow="-107" windowWidth="20847" windowHeight="12401" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="172">
   <si>
     <t>К5-К2</t>
   </si>
@@ -549,13 +549,19 @@
   </si>
   <si>
     <t>4610231970711</t>
+  </si>
+  <si>
+    <t>Retort В 300</t>
+  </si>
+  <si>
+    <t>Retort В 200</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,6 +579,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF77767E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -595,7 +608,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -633,11 +646,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -645,11 +669,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -936,12 +973,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.69921875" customWidth="1"/>
-    <col min="2" max="2" width="16.8984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.09765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -1902,9 +1939,47 @@
         <v>169</v>
       </c>
     </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B60" s="7">
+        <v>2048945897499</v>
+      </c>
+      <c r="C60" s="7">
+        <v>4610231972418</v>
+      </c>
+      <c r="D60" s="7">
+        <v>4610231972418</v>
+      </c>
+      <c r="E60" s="7">
+        <v>4610231972418</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B61" s="7">
+        <v>2047555679853</v>
+      </c>
+      <c r="C61" s="7">
+        <v>4610231972418</v>
+      </c>
+      <c r="D61" s="7">
+        <v>4610231972418</v>
+      </c>
+      <c r="E61" s="7"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B62" s="5"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B19:B59">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B60:E61">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
